--- a/research/iterations/a03c-s2/qualified-results.xlsx
+++ b/research/iterations/a03c-s2/qualified-results.xlsx
@@ -1732,10 +1732,10 @@
         <v>0</v>
       </c>
       <c r="T2">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="U2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="V2">
         <v>50</v>
@@ -1797,13 +1797,13 @@
         <v>0.4</v>
       </c>
       <c r="S3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T3">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="U3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="V3">
         <v>50</v>
